--- a/public/samples/S01_固定資産台帳_2026年3月期.xlsx
+++ b/public/samples/S01_固定資産台帳_2026年3月期.xlsx
@@ -768,7 +768,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="1">
-        <v>41730</v>
+        <v>42461</v>
       </c>
       <c r="E9" s="2">
         <v>20000000</v>
@@ -777,10 +777,10 @@
         <v>10</v>
       </c>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="H9" s="2">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
